--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104505_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104505_W6.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8175</v>
+        <v>2.6602</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8548</v>
+        <v>2.0783</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9627</v>
+        <v>0.5819</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9611</v>
+        <v>1.9653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9828</v>
+        <v>0.9741</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9784</v>
+        <v>0.9912</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5523</v>
+        <v>1.5316</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4404</v>
+        <v>1.4199</v>
       </c>
       <c r="L2" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4088</v>
+        <v>0.4336</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4708</v>
+        <v>0.3079</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8903</v>
+        <v>1.1401</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4195</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3797</v>
+        <v>2.1936</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7872</v>
+        <v>2.6637</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4074</v>
+        <v>-0.4701</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9917</v>
+        <v>1.0008</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3679</v>
+        <v>0.3704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6238</v>
+        <v>0.6304</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1925</v>
+        <v>-0.2093</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1842</v>
+        <v>1.2101</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9651</v>
+        <v>0.9809</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.973</v>
+        <v>-0.1729</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0212</v>
+        <v>0.9217</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9942</v>
+        <v>-1.0947</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2586</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8538</v>
+        <v>-0.9273</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5952</v>
+        <v>1.6123</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3986</v>
+        <v>1.59</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3739</v>
+        <v>1.7377</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7725</v>
+        <v>-0.1476</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7385</v>
+        <v>0.8971</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6264999999999999</v>
+        <v>1.7097</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112</v>
+        <v>-0.8126</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1371</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2526</v>
+        <v>0.028</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8844</v>
+        <v>0.665</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1936</v>
+        <v>1.1648</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4498</v>
+        <v>1.4535</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2562</v>
+        <v>-0.2887</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1441</v>
+        <v>-0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>-0.7739</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1093</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5293</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7242</v>
+        <v>0.9863</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3608</v>
+        <v>-0.457</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5948</v>
+        <v>0.2587</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7388</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.144</v>
+        <v>0.3248</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9301</v>
+        <v>0.8888</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7246</v>
+        <v>0.293</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7945</v>
+        <v>0.5958</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6647</v>
+        <v>-0.6301</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0142</v>
+        <v>-0.3592</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6505</v>
+        <v>-0.271</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1079</v>
+        <v>0.2706</v>
       </c>
       <c r="T5" t="n">
-        <v>1.612</v>
+        <v>0.0975</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5042</v>
+        <v>0.1732</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5078</v>
+        <v>0.0215</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7523</v>
+        <v>-0.2715</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2445</v>
+        <v>0.293</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2547</v>
+        <v>-0.6054</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0678</v>
+        <v>0.3242</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3225</v>
+        <v>-0.9296</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8915</v>
+        <v>-1.3809</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2944</v>
+        <v>0.9136</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5971</v>
+        <v>-2.2945</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6368</v>
+        <v>0.7755</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3622</v>
+        <v>-0.5893</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2745</v>
+        <v>1.3648</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2531</v>
+        <v>0.8757</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1391</v>
+        <v>0.8637</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3923</v>
+        <v>0.0119</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.4733</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5917</v>
+        <v>0.0098</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7937</v>
+        <v>0.4104</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2021</v>
+        <v>-0.4006</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6088</v>
+        <v>0.1304</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3188</v>
+        <v>-0.8185</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9276</v>
+        <v>0.9489</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3667</v>
+        <v>-0.5466</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9177999999999999</v>
+        <v>-0.7174</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.2844</v>
+        <v>0.1708</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7578</v>
+        <v>0.677</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.599</v>
+        <v>-0.1011</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3568</v>
+        <v>0.778</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2686</v>
+        <v>-0.706</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3176</v>
+        <v>0.1925</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.049</v>
+        <v>-0.8986</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9320000000000001</v>
+        <v>2.1789</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4822</v>
+        <v>3.2684</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4141</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9473</v>
+        <v>-0.2944</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2116</v>
+        <v>1.0602</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7356</v>
+        <v>-1.3546</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1308</v>
+        <v>-1.3965</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8181</v>
+        <v>0.3652</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9489</v>
+        <v>-1.7617</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5256999999999999</v>
+        <v>0.7215</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7069</v>
+        <v>0.6098</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1812</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6565</v>
+        <v>-2.118</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1113</v>
+        <v>-0.2446</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7678</v>
+        <v>-1.8734</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5878</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6755</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4688</v>
+        <v>0.6848</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2068</v>
+        <v>-0.0381</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1853</v>
+        <v>1.1383</v>
       </c>
       <c r="W8" t="n">
-        <v>3.278</v>
+        <v>1.2472</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0057</v>
+        <v>-1.8679</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6345</v>
+        <v>1.9652</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.6402</v>
+        <v>-3.8331</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.719</v>
+        <v>-3.7125</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7172</v>
+        <v>-1.712</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0018</v>
+        <v>-2.0005</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1448</v>
+        <v>0.1279</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.111</v>
+        <v>-0.1174</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.8638</v>
+        <v>-3.8405</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6062</v>
+        <v>-1.5946</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2576</v>
+        <v>-2.2458</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0433</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4255</v>
+        <v>0.2058</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5297</v>
+        <v>1.5253</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2267</v>
+        <v>-3.2239</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7793</v>
+        <v>-1.6221</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4474</v>
+        <v>-1.6018</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.4478</v>
+        <v>-5.4379</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.215</v>
+        <v>-1.2122</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.2328</v>
+        <v>-4.2257</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7408</v>
+        <v>-2.7623</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5683</v>
+        <v>-0.5795</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1725</v>
+        <v>-2.1827</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.707</v>
+        <v>-2.6756</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0603</v>
+        <v>-2.043</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6696</v>
+        <v>0.3229</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9043</v>
+        <v>0.2783</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2347</v>
+        <v>0.0446</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5207</v>
+        <v>-4.1403</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0657</v>
+        <v>-0.8627</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4551</v>
+        <v>-3.2777</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0438</v>
+        <v>-1.0455</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.489</v>
+        <v>-1.4987</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4452</v>
+        <v>0.4532</v>
       </c>
       <c r="J11" t="n">
-        <v>1.986</v>
+        <v>1.962</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4023</v>
+        <v>-0.4212</v>
       </c>
       <c r="L11" t="n">
-        <v>2.3883</v>
+        <v>2.3832</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.0298</v>
+        <v>-3.0075</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.553</v>
+        <v>-1.1648</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9966</v>
+        <v>-0.8441</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.106</v>
+        <v>-6.0164</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7997</v>
+        <v>-2.898</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3063</v>
+        <v>-3.1184</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8442</v>
+        <v>-1.832</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.834</v>
+        <v>-0.833</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0101</v>
+        <v>-0.999</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2787</v>
+        <v>1.258</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3605</v>
+        <v>-0.3727</v>
       </c>
       <c r="L12" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1229</v>
+        <v>-3.0901</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.6494</v>
+        <v>-2.6298</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3161</v>
+        <v>-0.5911</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5243</v>
+        <v>0.4665</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2083</v>
+        <v>-1.0576</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0515</v>
+        <v>0.0488</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.7979</v>
+        <v>-9.4435</v>
       </c>
       <c r="E13" t="n">
-        <v>2.508399999999998</v>
+        <v>2.582500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.3061</v>
+        <v>-12.0261</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.129099999999999</v>
+        <v>-9.0846</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.358900000000001</v>
+        <v>-2.369</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.77</v>
+        <v>-6.7156</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6962</v>
+        <v>2.4878</v>
       </c>
       <c r="K13" t="n">
-        <v>3.003400000000001</v>
+        <v>2.8789</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3070999999999999</v>
+        <v>-0.3910000000000011</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.8254</v>
+        <v>-11.5726</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.362399999999999</v>
+        <v>-5.2478</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.4627</v>
+        <v>-6.3248</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.6709</v>
+        <v>-5.6909</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8783</v>
+        <v>-15.934</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6957000000000004</v>
+        <v>1.0456</v>
       </c>
       <c r="T13" t="n">
-        <v>5.2777</v>
+        <v>5.6638</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.5823</v>
+        <v>-4.6185</v>
       </c>
       <c r="V13" t="n">
-        <v>4.3063</v>
+        <v>4.2865</v>
       </c>
       <c r="W13" t="n">
-        <v>10.4127</v>
+        <v>10.3648</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.1063</v>
+        <v>-6.0783</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3137</v>
+        <v>4.9471</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6392</v>
+        <v>5.2484</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3255</v>
+        <v>-0.3014</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5686</v>
+        <v>3.551</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7761</v>
+        <v>-0.7864</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3448</v>
+        <v>4.3374</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2935</v>
+        <v>3.2625</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6967</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9902</v>
+        <v>3.9767</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2751</v>
+        <v>0.2886</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6109</v>
+        <v>0.2579</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3871</v>
+        <v>0.0346</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2238</v>
+        <v>0.2232</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1327</v>
+        <v>4.4847</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1821</v>
+        <v>4.4405</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0494</v>
+        <v>0.0442</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3312</v>
+        <v>3.3208</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1588</v>
+        <v>1.1521</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1724</v>
+        <v>2.1687</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0369</v>
+        <v>3.003</v>
       </c>
       <c r="K15" t="n">
-        <v>1.475</v>
+        <v>1.4544</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5619</v>
+        <v>1.5486</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2943</v>
+        <v>0.3178</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3744</v>
+        <v>-0.2717</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0525</v>
+        <v>0.348</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6781</v>
+        <v>-0.6198</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1742</v>
+        <v>3.7159</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3514</v>
+        <v>5.8043</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1772</v>
+        <v>-2.0884</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3432</v>
+        <v>5.0215</v>
       </c>
       <c r="H16" t="n">
-        <v>2.101</v>
+        <v>2.1709</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2422</v>
+        <v>2.8506</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3021</v>
+        <v>5.3904</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5109</v>
+        <v>2.5166</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7912</v>
+        <v>2.8738</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.959</v>
+        <v>-0.3689</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4099</v>
+        <v>-0.3457</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.549</v>
+        <v>-0.0232</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6457000000000001</v>
+        <v>-0.8582</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7712</v>
+        <v>-0.0609</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1255</v>
+        <v>-0.7973</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>-2.7237</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0.7025</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5763</v>
+        <v>3.2494</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9012</v>
+        <v>3.5675</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3249</v>
+        <v>-0.3182</v>
       </c>
       <c r="G17" t="n">
-        <v>5.027</v>
+        <v>3.3423</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1643</v>
+        <v>2.0968</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8627</v>
+        <v>1.2455</v>
       </c>
       <c r="J17" t="n">
-        <v>5.4281</v>
+        <v>4.2867</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5282</v>
+        <v>2.4993</v>
       </c>
       <c r="L17" t="n">
-        <v>2.8999</v>
+        <v>1.7874</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4011</v>
+        <v>-0.9444</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3639</v>
+        <v>-0.4025</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0372</v>
+        <v>-0.5419</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4952</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9874</v>
+        <v>0.7281</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0071</v>
+        <v>1.0124</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9802</v>
+        <v>-0.2843</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.7317</v>
+        <v>0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.4387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>L. LABEYRIE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7839</v>
+        <v>0.76</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8317</v>
+        <v>-0.0057</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9522</v>
+        <v>0.7657</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2086</v>
+        <v>-0.8728</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7257</v>
+        <v>-1.2439</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5171</v>
+        <v>0.3711</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1532</v>
+        <v>-0.3023</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.7876</v>
+        <v>-1.1139</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6344</v>
+        <v>0.8115</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0554</v>
+        <v>-0.5704</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0619</v>
+        <v>-0.13</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1172</v>
+        <v>-0.4405</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3101</v>
+        <v>0.446</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8903</v>
+        <v>0.3665</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4198</v>
+        <v>0.0795</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2249</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3214</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. LABEYRIE</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8796</v>
+        <v>0.1995</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.226</v>
+        <v>-0.3641</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1056</v>
+        <v>0.5636</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8804</v>
+        <v>-1.2088</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2482</v>
+        <v>-1.7288</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3679</v>
+        <v>0.52</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2869</v>
+        <v>-1.1671</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1052</v>
+        <v>-1.8001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8183</v>
+        <v>0.633</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5935</v>
+        <v>-0.0417</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1431</v>
+        <v>0.0713</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4504</v>
+        <v>-0.113</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5843</v>
+        <v>0.727</v>
       </c>
       <c r="T19" t="n">
-        <v>0.127</v>
+        <v>0.7151</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4573</v>
+        <v>0.0119</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-0.2292</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1914</v>
+        <v>-0.0489</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6774</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4859</v>
+        <v>-0.1243</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2101</v>
+        <v>-1.2102</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0534</v>
+        <v>0.0545</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2635</v>
+        <v>-1.2647</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7925</v>
+        <v>-0.8093</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4176</v>
+        <v>-0.4009</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.721</v>
+        <v>0.4784</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4699</v>
+        <v>0.8847</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7489</v>
+        <v>-0.4063</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9791</v>
+        <v>-1.7231</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7114</v>
+        <v>-2.9232</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7323</v>
+        <v>1.2001</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1431</v>
+        <v>-3.1535</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7649</v>
+        <v>-1.7554</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3782</v>
+        <v>-1.3981</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1497</v>
+        <v>-3.1831</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4169</v>
+        <v>-1.4242</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7328</v>
+        <v>-1.7589</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0065</v>
+        <v>0.0296</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9928</v>
+        <v>-0.7305</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5202</v>
+        <v>0.3085</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4726</v>
+        <v>-1.0391</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7032</v>
+        <v>1.7057</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0686</v>
+        <v>-1.9583</v>
       </c>
       <c r="E22" t="n">
+        <v>-3.5182</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.5599</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.2054</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.9588</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.3021</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.9308</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.09669999999999999</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.1246</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-2.2763</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-4.7803</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.5039</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.8874</v>
+      </c>
+      <c r="T22" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F22" t="n">
-        <v>-3.0285</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.9091</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.4472</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-2.3564</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-0.1852</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.2512</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-2.4364</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-0.7239</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.8038999999999999</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="U22" t="n">
+        <v>-0.8474</v>
+      </c>
+      <c r="V22" t="n">
         <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-1.1342</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.1342</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.1866</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.2794</v>
-      </c>
-      <c r="U22" t="n">
-        <v>-1.0927</v>
-      </c>
-      <c r="V22" t="n">
-        <v>-2.3461</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2065</v>
+        <v>-3.0446</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2994</v>
+        <v>-0.299</v>
       </c>
       <c r="F23" t="n">
-        <v>1.093</v>
+        <v>-2.7456</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2104</v>
+        <v>-0.911</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9493</v>
+        <v>1.4502</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2611</v>
+        <v>-2.3613</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3321</v>
+        <v>-0.2103</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9351</v>
+        <v>2.2408</v>
       </c>
       <c r="L23" t="n">
-        <v>0.397</v>
+        <v>-2.4511</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1216</v>
+        <v>-0.7007</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0142</v>
+        <v>-0.7906</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1359</v>
+        <v>0.0898</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.7635</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1486</v>
+        <v>0.2031</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.868</v>
+        <v>1.0494</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2806</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.797599999999997</v>
+        <v>10.5817</v>
       </c>
       <c r="E24" t="n">
-        <v>12.3062</v>
+        <v>12.0259</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5083</v>
+        <v>-1.4444</v>
       </c>
       <c r="G24" t="n">
-        <v>9.129099999999999</v>
+        <v>9.0847</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3591</v>
+        <v>2.3688</v>
       </c>
       <c r="I24" t="n">
-        <v>6.770099999999999</v>
+        <v>6.715800000000002</v>
       </c>
       <c r="J24" t="n">
-        <v>11.8252</v>
+        <v>11.5726</v>
       </c>
       <c r="K24" t="n">
-        <v>5.3622</v>
+        <v>5.247800000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>6.462900000000002</v>
+        <v>6.324699999999998</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6962</v>
+        <v>-2.4877</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.0033</v>
+        <v>-2.8789</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3073000000000001</v>
+        <v>0.3910999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>5.670800000000001</v>
+        <v>5.690799999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-10.2074</v>
+        <v>-10.2434</v>
       </c>
       <c r="R24" t="n">
-        <v>15.8784</v>
+        <v>15.9341</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6957999999999998</v>
+        <v>0.09270000000000017</v>
       </c>
       <c r="T24" t="n">
-        <v>4.5821</v>
+        <v>4.618300000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.277699999999999</v>
+        <v>-4.5259</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.3066</v>
+        <v>-4.2865</v>
       </c>
       <c r="W24" t="n">
-        <v>6.106199999999999</v>
+        <v>6.078399999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-10.4127</v>
+        <v>-10.3647</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104505_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104505_W6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.0783</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104505_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-10.3647</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
